--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:09</t>
+    <t xml:space="preserve">2026-09-09 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:06</t>
+    <t xml:space="preserve">2026-09-17 13:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>354870.44</v>
+        <v>417681.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>417681.09</v>
+        <v>354870.44</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>317973.06</v>
+        <v>376639.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>354870.44</v>
+        <v>417681.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>364318.84</v>
+        <v>430151.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>376639.38</v>
+        <v>317973.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>417681.09</v>
+        <v>354870.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>430151.56</v>
+        <v>364318.84</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:35</t>
+    <t xml:space="preserve">2026-09-25 21:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,7 +527,7 @@
         <v>221778.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>52061.26</v>
+        <v>52061.27</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>23.47</v>
@@ -573,7 +573,7 @@
         <v>265048.88</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50239.9</v>
+        <v>50239.91</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>18.95</v>
@@ -780,7 +780,7 @@
         <v>344231.88</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37629.96</v>
+        <v>37629.97</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10.93</v>
@@ -826,7 +826,7 @@
         <v>447030.59</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45195.6</v>
+        <v>45195.59</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>10.11</v>
@@ -849,7 +849,7 @@
         <v>376639.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41041.71</v>
+        <v>41041.72</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>10.9</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:36</t>
+    <t xml:space="preserve">2026-10-05 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
